--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MELILLA CIUDAD DEL DEPORTE.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MELILLA CIUDAD DEL DEPORTE.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>19.5249</v>
+        <v>14.5602</v>
       </c>
       <c r="E2" t="n">
-        <v>15.6344</v>
+        <v>21.1111</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8908</v>
+        <v>-6.551</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.2905</v>
+        <v>16.4035</v>
       </c>
       <c r="H2" t="n">
-        <v>-19.1225</v>
+        <v>2.3607</v>
       </c>
       <c r="I2" t="n">
-        <v>11.8318</v>
+        <v>14.0431</v>
       </c>
       <c r="J2" t="n">
-        <v>27.6687</v>
+        <v>28.8015</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7849</v>
+        <v>11.0312</v>
       </c>
       <c r="L2" t="n">
-        <v>24.8843</v>
+        <v>17.7702</v>
       </c>
       <c r="M2" t="n">
-        <v>-34.9596</v>
+        <v>-12.3981</v>
       </c>
       <c r="N2" t="n">
-        <v>-21.907</v>
+        <v>-8.6707</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.0524</v>
+        <v>-3.7272</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5225</v>
+        <v>-7.8303</v>
       </c>
       <c r="Q2" t="n">
-        <v>-33.496</v>
+        <v>-21.9681</v>
       </c>
       <c r="R2" t="n">
-        <v>35.0185</v>
+        <v>14.1378</v>
       </c>
       <c r="S2" t="n">
-        <v>23.9062</v>
+        <v>-2.4258</v>
       </c>
       <c r="T2" t="n">
-        <v>10.3156</v>
+        <v>-1.9324</v>
       </c>
       <c r="U2" t="n">
-        <v>13.5904</v>
+        <v>-0.4937999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3866</v>
+        <v>8.412700000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>11.1459</v>
+        <v>16.2101</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.7592</v>
+        <v>-7.7974</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>10.4678</v>
+        <v>4.364400000000002</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>7.706300000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.5322</v>
+        <v>-3.342</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4035</v>
+        <v>-7.2905</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3607</v>
+        <v>-19.1225</v>
       </c>
       <c r="I3" t="n">
-        <v>14.0431</v>
+        <v>11.8318</v>
       </c>
       <c r="J3" t="n">
-        <v>28.8015</v>
+        <v>27.6687</v>
       </c>
       <c r="K3" t="n">
-        <v>11.0312</v>
+        <v>2.7849</v>
       </c>
       <c r="L3" t="n">
-        <v>17.7702</v>
+        <v>24.8843</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.3981</v>
+        <v>-34.9596</v>
       </c>
       <c r="N3" t="n">
-        <v>-8.6707</v>
+        <v>-21.907</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.7272</v>
+        <v>-13.0524</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.8303</v>
+        <v>1.5225</v>
       </c>
       <c r="Q3" t="n">
-        <v>-21.9681</v>
+        <v>-33.496</v>
       </c>
       <c r="R3" t="n">
-        <v>14.1378</v>
+        <v>35.0185</v>
       </c>
       <c r="S3" t="n">
-        <v>-6.5183</v>
+        <v>8.745600000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.0433</v>
+        <v>2.3879</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.475</v>
+        <v>6.3574</v>
       </c>
       <c r="V3" t="n">
-        <v>8.412700000000001</v>
+        <v>1.3866</v>
       </c>
       <c r="W3" t="n">
-        <v>16.2101</v>
+        <v>11.1459</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.7974</v>
+        <v>-9.7592</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>7.783399999999999</v>
+        <v>2.001300000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>15.4455</v>
+        <v>2.138599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.6619</v>
+        <v>-0.1371999999999995</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.4483</v>
+        <v>-7.6548</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.132</v>
+        <v>-11.5909</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.3162</v>
+        <v>3.9361</v>
       </c>
       <c r="J4" t="n">
-        <v>8.994899999999999</v>
+        <v>9.744</v>
       </c>
       <c r="K4" t="n">
-        <v>5.336499999999999</v>
+        <v>5.1745</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6583</v>
+        <v>4.5693</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.443</v>
+        <v>-17.3986</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.4687</v>
+        <v>-16.7656</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.974299999999999</v>
+        <v>-0.6332000000000004</v>
       </c>
       <c r="P4" t="n">
-        <v>-9.7879</v>
+        <v>8.264999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-28.7107</v>
+        <v>-11.5278</v>
       </c>
       <c r="R4" t="n">
-        <v>18.9227</v>
+        <v>19.7928</v>
       </c>
       <c r="S4" t="n">
-        <v>26.8072</v>
+        <v>1.3702</v>
       </c>
       <c r="T4" t="n">
-        <v>21.2824</v>
+        <v>-0.2283</v>
       </c>
       <c r="U4" t="n">
-        <v>5.5249</v>
+        <v>1.5985</v>
       </c>
       <c r="V4" t="n">
-        <v>4.2122</v>
+        <v>0.02020000000000044</v>
       </c>
       <c r="W4" t="n">
-        <v>13.879</v>
+        <v>4.1501</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.6668</v>
+        <v>-4.129899999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. POIRIER</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>4.970299999999999</v>
+        <v>-0.4610999999999996</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1344999999999992</v>
+        <v>-5.6355</v>
       </c>
       <c r="F5" t="n">
-        <v>4.835799999999999</v>
+        <v>5.1743</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9602</v>
+        <v>-4.223600000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1189</v>
+        <v>-1.542999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>8.0792</v>
+        <v>-2.680400000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>21.4148</v>
+        <v>8.1654</v>
       </c>
       <c r="K5" t="n">
-        <v>9.9655</v>
+        <v>5.8516</v>
       </c>
       <c r="L5" t="n">
-        <v>11.4495</v>
+        <v>2.3136</v>
       </c>
       <c r="M5" t="n">
-        <v>-15.4548</v>
+        <v>-12.389</v>
       </c>
       <c r="N5" t="n">
-        <v>-12.0845</v>
+        <v>-7.394699999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.370400000000001</v>
+        <v>-4.9943</v>
       </c>
       <c r="P5" t="n">
-        <v>-15.8782</v>
+        <v>4.5677</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.7135</v>
+        <v>-20.4457</v>
       </c>
       <c r="R5" t="n">
-        <v>17.8353</v>
+        <v>25.0132</v>
       </c>
       <c r="S5" t="n">
-        <v>11.2413</v>
+        <v>-3.9278</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.05859999999999987</v>
+        <v>-1.6762</v>
       </c>
       <c r="U5" t="n">
-        <v>11.3</v>
+        <v>-2.2516</v>
       </c>
       <c r="V5" t="n">
-        <v>3.6468</v>
+        <v>3.1226</v>
       </c>
       <c r="W5" t="n">
-        <v>12.4919</v>
+        <v>8.3208</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.844999999999999</v>
+        <v>-5.198399999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7447</v>
+        <v>-2.4904</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4734</v>
+        <v>-0.2499</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2713</v>
+        <v>-2.2405</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3493</v>
@@ -922,13 +922,13 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4829</v>
+        <v>-0.2287</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2055</v>
+        <v>0.0181</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2775</v>
+        <v>-0.2466</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>D. POIRIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.9116</v>
+        <v>-4.093399999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0238</v>
+        <v>-2.024999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.8878</v>
+        <v>-2.0684</v>
       </c>
       <c r="G7" t="n">
-        <v>-15.0996</v>
+        <v>5.9602</v>
       </c>
       <c r="H7" t="n">
-        <v>-8.898200000000001</v>
+        <v>-2.1189</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.2012</v>
+        <v>8.0792</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.7711</v>
+        <v>21.4148</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.948799999999999</v>
+        <v>9.9655</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1776</v>
+        <v>11.4495</v>
       </c>
       <c r="M7" t="n">
-        <v>-10.3284</v>
+        <v>-15.4548</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.9495</v>
+        <v>-12.0845</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.3791</v>
+        <v>-3.370400000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-6.5251</v>
+        <v>-15.8782</v>
       </c>
       <c r="Q7" t="n">
-        <v>-14.1379</v>
+        <v>-33.7135</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6126</v>
+        <v>17.8353</v>
       </c>
       <c r="S7" t="n">
-        <v>13.8883</v>
+        <v>2.1775</v>
       </c>
       <c r="T7" t="n">
-        <v>11.0642</v>
+        <v>-2.218</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8241</v>
+        <v>4.3959</v>
       </c>
       <c r="V7" t="n">
-        <v>2.8249</v>
+        <v>3.6468</v>
       </c>
       <c r="W7" t="n">
-        <v>6.8213</v>
+        <v>12.4919</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.9963</v>
+        <v>-8.844999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.366200000000001</v>
+        <v>-8.703999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1603</v>
+        <v>1.525900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.2058</v>
+        <v>-10.23</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.6548</v>
+        <v>-13.4483</v>
       </c>
       <c r="H8" t="n">
-        <v>-11.5909</v>
+        <v>-9.132</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9361</v>
+        <v>-4.3162</v>
       </c>
       <c r="J8" t="n">
-        <v>9.744</v>
+        <v>8.994899999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1745</v>
+        <v>5.336499999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>4.5693</v>
+        <v>3.6583</v>
       </c>
       <c r="M8" t="n">
-        <v>-17.3986</v>
+        <v>-22.443</v>
       </c>
       <c r="N8" t="n">
-        <v>-16.7656</v>
+        <v>-14.4687</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6332000000000004</v>
+        <v>-7.974299999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>8.264999999999999</v>
+        <v>-9.7879</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.5278</v>
+        <v>-28.7107</v>
       </c>
       <c r="R8" t="n">
-        <v>19.7928</v>
+        <v>18.9227</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.9976</v>
+        <v>10.3195</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.527</v>
+        <v>7.3631</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.4704</v>
+        <v>2.9568</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02020000000000044</v>
+        <v>4.2122</v>
       </c>
       <c r="W8" t="n">
-        <v>4.1501</v>
+        <v>13.879</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.129899999999999</v>
+        <v>-9.6668</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CAICEDO SANCHEZ</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.9801</v>
+        <v>-10.0938</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.8284</v>
+        <v>-1.8758</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8483999999999998</v>
+        <v>-8.2181</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.014200000000001</v>
+        <v>-15.8107</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.548100000000001</v>
+        <v>-10.9554</v>
       </c>
       <c r="I9" t="n">
-        <v>2.534</v>
+        <v>-4.8551</v>
       </c>
       <c r="J9" t="n">
-        <v>11.788</v>
+        <v>10.3574</v>
       </c>
       <c r="K9" t="n">
-        <v>4.478199999999999</v>
+        <v>4.778799999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>7.309900000000001</v>
+        <v>5.5784</v>
       </c>
       <c r="M9" t="n">
-        <v>-15.8023</v>
+        <v>-26.1679</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.0264</v>
+        <v>-15.7342</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.7761</v>
+        <v>-10.4337</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.8727</v>
+        <v>-1.0877</v>
       </c>
       <c r="Q9" t="n">
-        <v>-30.0159</v>
+        <v>-25.2308</v>
       </c>
       <c r="R9" t="n">
         <v>24.1432</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5159</v>
+        <v>4.5752</v>
       </c>
       <c r="T9" t="n">
-        <v>3.0573</v>
+        <v>2.0058</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4585999999999998</v>
+        <v>2.5693</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.609</v>
+        <v>2.229200000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>5.3421</v>
+        <v>10.9919</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.951099999999999</v>
+        <v>-8.7628</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>J. BERGSTEDT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.161900000000001</v>
+        <v>-10.9858</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01679999999999926</v>
+        <v>-6.6511</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.179</v>
+        <v>-4.3348</v>
       </c>
       <c r="G10" t="n">
-        <v>-15.8107</v>
+        <v>-8.6793</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.9554</v>
+        <v>-4.7499</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.8551</v>
+        <v>-3.9295</v>
       </c>
       <c r="J10" t="n">
-        <v>10.3574</v>
+        <v>-3.821</v>
       </c>
       <c r="K10" t="n">
-        <v>4.778799999999999</v>
+        <v>-2.3709</v>
       </c>
       <c r="L10" t="n">
-        <v>5.5784</v>
+        <v>-1.4503</v>
       </c>
       <c r="M10" t="n">
-        <v>-26.1679</v>
+        <v>-4.8581</v>
       </c>
       <c r="N10" t="n">
-        <v>-15.7342</v>
+        <v>-2.3791</v>
       </c>
       <c r="O10" t="n">
-        <v>-10.4337</v>
+        <v>-2.4791</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0877</v>
+        <v>-2.6102</v>
       </c>
       <c r="Q10" t="n">
-        <v>-25.2308</v>
+        <v>-6.5252</v>
       </c>
       <c r="R10" t="n">
-        <v>24.1432</v>
+        <v>3.915</v>
       </c>
       <c r="S10" t="n">
-        <v>5.5071</v>
+        <v>2.7172</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8985</v>
+        <v>1.394</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6087</v>
+        <v>1.3233</v>
       </c>
       <c r="V10" t="n">
-        <v>2.229200000000001</v>
+        <v>-2.4138</v>
       </c>
       <c r="W10" t="n">
-        <v>10.9919</v>
+        <v>2.3013</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.7628</v>
+        <v>-4.715199999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BERGSTEDT</t>
+          <t>M. CAICEDO SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.6851</v>
+        <v>-11.6895</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.601699999999999</v>
+        <v>-12.1681</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.0831</v>
+        <v>0.4790000000000006</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.6793</v>
+        <v>-4.014200000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.7499</v>
+        <v>-6.548100000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.9295</v>
+        <v>2.534</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.821</v>
+        <v>11.788</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3709</v>
+        <v>4.478199999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4503</v>
+        <v>7.309900000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.8581</v>
+        <v>-15.8023</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.3791</v>
+        <v>-11.0264</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4791</v>
+        <v>-4.7761</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.6102</v>
+        <v>-5.8727</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.5252</v>
+        <v>-30.0159</v>
       </c>
       <c r="R11" t="n">
-        <v>3.915</v>
+        <v>24.1432</v>
       </c>
       <c r="S11" t="n">
-        <v>4.0182</v>
+        <v>0.8067000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>2.443</v>
+        <v>0.7175999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>1.575</v>
+        <v>0.08909999999999985</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4138</v>
+        <v>-2.609</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3013</v>
+        <v>5.3421</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.715199999999999</v>
+        <v>-7.951099999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.0156</v>
+        <v>-13.8486</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.6332</v>
+        <v>-8.013999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6174000000000002</v>
+        <v>-5.8347</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.223600000000001</v>
+        <v>-15.0996</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.542999999999999</v>
+        <v>-8.898200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.680400000000001</v>
+        <v>-6.2012</v>
       </c>
       <c r="J12" t="n">
-        <v>8.1654</v>
+        <v>-4.7711</v>
       </c>
       <c r="K12" t="n">
-        <v>5.8516</v>
+        <v>-4.948799999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.3136</v>
+        <v>0.1776</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.389</v>
+        <v>-10.3284</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.394699999999999</v>
+        <v>-3.9495</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.9943</v>
+        <v>-6.3791</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5677</v>
+        <v>-6.5251</v>
       </c>
       <c r="Q12" t="n">
-        <v>-20.4457</v>
+        <v>-14.1379</v>
       </c>
       <c r="R12" t="n">
-        <v>25.0132</v>
+        <v>7.6126</v>
       </c>
       <c r="S12" t="n">
-        <v>-15.4822</v>
+        <v>4.9511</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.6737</v>
+        <v>4.0738</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.8083</v>
+        <v>0.8771</v>
       </c>
       <c r="V12" t="n">
-        <v>3.1226</v>
+        <v>2.8249</v>
       </c>
       <c r="W12" t="n">
-        <v>8.3208</v>
+        <v>6.8213</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.198399999999999</v>
+        <v>-3.9963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. PENO</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.7143</v>
+        <v>-18.8467</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.1858</v>
+        <v>-0.4592000000000018</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.528600000000001</v>
+        <v>-18.3879</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.809699999999999</v>
+        <v>-19.3498</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.742100000000001</v>
+        <v>-30.0032</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9323</v>
+        <v>10.6532</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7192999999999999</v>
+        <v>22.1476</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.3397</v>
+        <v>-3.3869</v>
       </c>
       <c r="L13" t="n">
-        <v>3.6201</v>
+        <v>25.5345</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.0905</v>
+        <v>-41.4979</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.402699999999999</v>
+        <v>-26.6165</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.6879</v>
+        <v>-14.8813</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.6552</v>
+        <v>-24.3607</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6153</v>
+        <v>-69.6019</v>
       </c>
       <c r="R13" t="n">
-        <v>6.96</v>
+        <v>45.2412</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.7288</v>
+        <v>-0.9805999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1113</v>
+        <v>-0.1761</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.6176</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5204</v>
+        <v>25.8451</v>
       </c>
       <c r="W13" t="n">
-        <v>2.26</v>
+        <v>47.1717</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.7804</v>
+        <v>-21.3267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.264</v>
+        <v>-18.962</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.8895</v>
+        <v>-7.9321</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.3744</v>
+        <v>-11.0298</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.1533</v>
+        <v>1.4899</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.5179</v>
+        <v>-3.1006</v>
       </c>
       <c r="I14" t="n">
-        <v>-10.6357</v>
+        <v>4.5907</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.1529</v>
+        <v>22.4021</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9737</v>
+        <v>12.2751</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.1266</v>
+        <v>10.1268</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.0005</v>
+        <v>-20.9119</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.4915</v>
+        <v>-15.3758</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.5091</v>
+        <v>-5.536</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.8277</v>
+        <v>-23.0557</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.5305</v>
+        <v>-46.9813</v>
       </c>
       <c r="R14" t="n">
-        <v>13.7028</v>
+        <v>23.9257</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.6759</v>
+        <v>-5.7786</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3768</v>
+        <v>-3.9705</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.2992</v>
+        <v>-1.8085</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3931</v>
+        <v>8.382600000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1708</v>
+        <v>20.6173</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7777</v>
+        <v>-12.2349</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>S. PENO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>-27.2338</v>
+        <v>-19.5221</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.714</v>
+        <v>-12.0623</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.5202</v>
+        <v>-7.46</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4899</v>
+        <v>-8.809699999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.1006</v>
+        <v>-9.742100000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5907</v>
+        <v>0.9323</v>
       </c>
       <c r="J15" t="n">
-        <v>22.4021</v>
+        <v>-0.7192999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>12.2751</v>
+        <v>-4.3397</v>
       </c>
       <c r="L15" t="n">
-        <v>10.1268</v>
+        <v>3.6201</v>
       </c>
       <c r="M15" t="n">
-        <v>-20.9119</v>
+        <v>-8.0905</v>
       </c>
       <c r="N15" t="n">
-        <v>-15.3758</v>
+        <v>-5.402699999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.536</v>
+        <v>-2.6879</v>
       </c>
       <c r="P15" t="n">
-        <v>-23.0557</v>
+        <v>-5.6552</v>
       </c>
       <c r="Q15" t="n">
-        <v>-46.9813</v>
+        <v>-12.6153</v>
       </c>
       <c r="R15" t="n">
-        <v>23.9257</v>
+        <v>6.96</v>
       </c>
       <c r="S15" t="n">
-        <v>-14.0506</v>
+        <v>-3.5368</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.7521</v>
+        <v>-0.9879</v>
       </c>
       <c r="U15" t="n">
-        <v>-6.2987</v>
+        <v>-2.5491</v>
       </c>
       <c r="V15" t="n">
-        <v>8.382600000000002</v>
+        <v>-1.5204</v>
       </c>
       <c r="W15" t="n">
-        <v>20.6173</v>
+        <v>2.26</v>
       </c>
       <c r="X15" t="n">
-        <v>-12.2349</v>
+        <v>-3.7804</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. EZQUERRA TRELLES</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>-28.4363</v>
+        <v>-20.6102</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.3242</v>
+        <v>-15.6659</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.112299999999999</v>
+        <v>-4.9444</v>
       </c>
       <c r="G16" t="n">
-        <v>-15.3236</v>
+        <v>-16.1533</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.3249</v>
+        <v>-5.5179</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.9988</v>
+        <v>-10.6357</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.257099999999999</v>
+        <v>-1.1529</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.6499</v>
+        <v>2.9737</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6072</v>
+        <v>-4.1266</v>
       </c>
       <c r="M16" t="n">
-        <v>-8.0665</v>
+        <v>-15.0005</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.6749</v>
+        <v>-8.4915</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.3916</v>
+        <v>-6.5091</v>
       </c>
       <c r="P16" t="n">
-        <v>-11.0928</v>
+        <v>-2.8277</v>
       </c>
       <c r="Q16" t="n">
-        <v>-15.4429</v>
+        <v>-16.5305</v>
       </c>
       <c r="R16" t="n">
-        <v>4.35</v>
+        <v>13.7028</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2606000000000002</v>
+        <v>-4.0224</v>
       </c>
       <c r="T16" t="n">
-        <v>1.376</v>
+        <v>-2.1535</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1153</v>
+        <v>-1.8691</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.2806</v>
+        <v>2.3931</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.1708</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2806</v>
+        <v>-1.7777</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>-28.4723</v>
+        <v>-25.4316</v>
       </c>
       <c r="E17" t="n">
-        <v>-30.6557</v>
+        <v>-26.5313</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1836</v>
+        <v>1.099700000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-19.3437</v>
@@ -1780,13 +1780,13 @@
         <v>28.0579</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.6229</v>
+        <v>-0.5822999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.537100000000001</v>
+        <v>-2.4129</v>
       </c>
       <c r="U17" t="n">
-        <v>2.9137</v>
+        <v>1.8304</v>
       </c>
       <c r="V17" t="n">
         <v>-8.1158</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>J. EZQUERRA TRELLES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>-30.6274</v>
+        <v>-26.729</v>
       </c>
       <c r="E18" t="n">
-        <v>-25.6706</v>
+        <v>-20.8087</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.9566</v>
+        <v>-5.9203</v>
       </c>
       <c r="G18" t="n">
-        <v>-19.7335</v>
+        <v>-15.3236</v>
       </c>
       <c r="H18" t="n">
-        <v>-13.9365</v>
+        <v>-10.3249</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.797000000000001</v>
+        <v>-4.9988</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0851</v>
+        <v>-7.257099999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>3.0602</v>
+        <v>-6.6499</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.974899999999999</v>
+        <v>-0.6072</v>
       </c>
       <c r="M18" t="n">
-        <v>-20.8188</v>
+        <v>-8.0665</v>
       </c>
       <c r="N18" t="n">
-        <v>-16.9968</v>
+        <v>-3.6749</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.8219</v>
+        <v>-4.3916</v>
       </c>
       <c r="P18" t="n">
-        <v>-9.570399999999999</v>
+        <v>-11.0928</v>
       </c>
       <c r="Q18" t="n">
-        <v>-36.7583</v>
+        <v>-15.4429</v>
       </c>
       <c r="R18" t="n">
-        <v>27.1878</v>
+        <v>4.35</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1112</v>
+        <v>1.968</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7055999999999998</v>
+        <v>1.8916</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4056999999999997</v>
+        <v>0.07660000000000003</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4351</v>
+        <v>-2.2806</v>
       </c>
       <c r="W18" t="n">
-        <v>9.297000000000001</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-11.7319</v>
+        <v>-2.2806</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>-31.3601</v>
+        <v>-30.8858</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.4919</v>
+        <v>-25.5699</v>
       </c>
       <c r="F19" t="n">
-        <v>-15.868</v>
+        <v>-5.3161</v>
       </c>
       <c r="G19" t="n">
-        <v>-40.4527</v>
+        <v>-19.7335</v>
       </c>
       <c r="H19" t="n">
-        <v>-15.3925</v>
+        <v>-13.9365</v>
       </c>
       <c r="I19" t="n">
-        <v>-25.0603</v>
+        <v>-5.797000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.06990000000000129</v>
+        <v>1.0851</v>
       </c>
       <c r="K19" t="n">
-        <v>7.4319</v>
+        <v>3.0602</v>
       </c>
       <c r="L19" t="n">
-        <v>-7.501899999999999</v>
+        <v>-1.974899999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-40.3832</v>
+        <v>-20.8188</v>
       </c>
       <c r="N19" t="n">
-        <v>-22.8246</v>
+        <v>-16.9968</v>
       </c>
       <c r="O19" t="n">
-        <v>-17.5585</v>
+        <v>-3.8219</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4799</v>
+        <v>-9.570399999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-39.3685</v>
+        <v>-36.7583</v>
       </c>
       <c r="R19" t="n">
-        <v>42.8483</v>
+        <v>27.1878</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8871</v>
+        <v>0.8527000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>7.4168</v>
+        <v>0.8063999999999998</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.5297</v>
+        <v>0.04600000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>1.7257</v>
+        <v>-2.4351</v>
       </c>
       <c r="W19" t="n">
-        <v>16.5293</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>-14.8037</v>
+        <v>-11.7319</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>-37.3977</v>
+        <v>-32.1828</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.6256</v>
+        <v>-19.5622</v>
       </c>
       <c r="F20" t="n">
-        <v>-26.7721</v>
+        <v>-12.6207</v>
       </c>
       <c r="G20" t="n">
-        <v>-19.3498</v>
+        <v>-40.4527</v>
       </c>
       <c r="H20" t="n">
-        <v>-30.0032</v>
+        <v>-15.3925</v>
       </c>
       <c r="I20" t="n">
-        <v>10.6532</v>
+        <v>-25.0603</v>
       </c>
       <c r="J20" t="n">
-        <v>22.1476</v>
+        <v>-0.06990000000000129</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.3869</v>
+        <v>7.4319</v>
       </c>
       <c r="L20" t="n">
-        <v>25.5345</v>
+        <v>-7.501899999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-41.4979</v>
+        <v>-40.3832</v>
       </c>
       <c r="N20" t="n">
-        <v>-26.6165</v>
+        <v>-22.8246</v>
       </c>
       <c r="O20" t="n">
-        <v>-14.8813</v>
+        <v>-17.5585</v>
       </c>
       <c r="P20" t="n">
-        <v>-24.3607</v>
+        <v>3.4799</v>
       </c>
       <c r="Q20" t="n">
-        <v>-69.6019</v>
+        <v>-39.3685</v>
       </c>
       <c r="R20" t="n">
-        <v>45.2412</v>
+        <v>42.8483</v>
       </c>
       <c r="S20" t="n">
-        <v>-19.5316</v>
+        <v>3.0641</v>
       </c>
       <c r="T20" t="n">
-        <v>-10.3423</v>
+        <v>3.347</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.189</v>
+        <v>-0.2832</v>
       </c>
       <c r="V20" t="n">
-        <v>25.8451</v>
+        <v>1.7257</v>
       </c>
       <c r="W20" t="n">
-        <v>47.1717</v>
+        <v>16.5293</v>
       </c>
       <c r="X20" t="n">
-        <v>-21.3267</v>
+        <v>-14.8037</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>32</v>
       </c>
       <c r="D21" t="n">
-        <v>-58.0026</v>
+        <v>-39.0288</v>
       </c>
       <c r="E21" t="n">
-        <v>-39.14870000000001</v>
+        <v>-26.6173</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.8538</v>
+        <v>-12.4117</v>
       </c>
       <c r="G21" t="n">
         <v>-17.6373</v>
@@ -2092,13 +2092,13 @@
         <v>42.196</v>
       </c>
       <c r="S21" t="n">
-        <v>-25.4291</v>
+        <v>-6.4549</v>
       </c>
       <c r="T21" t="n">
-        <v>-17.9718</v>
+        <v>-5.4407</v>
       </c>
       <c r="U21" t="n">
-        <v>-7.4568</v>
+        <v>-1.0141</v>
       </c>
       <c r="V21" t="n">
         <v>-6.236</v>
@@ -2125,13 +2125,13 @@
         <v>32</v>
       </c>
       <c r="D22" t="n">
-        <v>-297.6273</v>
+        <v>-273.6397</v>
       </c>
       <c r="E22" t="n">
-        <v>-166.1956</v>
+        <v>-159.3464</v>
       </c>
       <c r="F22" t="n">
-        <v>-131.4311</v>
+        <v>-114.2946</v>
       </c>
       <c r="G22" t="n">
         <v>-210.5203</v>
@@ -2170,16 +2170,16 @@
         <v>425.2215</v>
       </c>
       <c r="S22" t="n">
-        <v>-10.3768</v>
+        <v>13.6099</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.040100000000008</v>
+        <v>2.808800000000002</v>
       </c>
       <c r="U22" t="n">
-        <v>-6.3364</v>
+        <v>10.7995</v>
       </c>
       <c r="V22" t="n">
-        <v>37.46100000000002</v>
+        <v>37.46100000000001</v>
       </c>
       <c r="W22" t="n">
         <v>203.4526</v>
